--- a/StructureDefinition-chul-location.xlsx
+++ b/StructureDefinition-chul-location.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-09-10T16:13:27+02:00</t>
+    <t>2025-09-12T12:04:03+02:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-chul-location.xlsx
+++ b/StructureDefinition-chul-location.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.1.2</t>
+    <t>0.2.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-09-12T12:04:03+02:00</t>
+    <t>2025-09-12T14:17:00+02:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -108,7 +108,7 @@
     <t>Base Definition</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/StructureDefinition/Location</t>
+    <t>http://hl7.eu/fhir/base/StructureDefinition/location-eu</t>
   </si>
   <si>
     <t>Abstract</t>
@@ -737,7 +737,7 @@
     <t>Location.name</t>
   </si>
   <si>
-    <t>Name of the location as used by humans</t>
+    <t>Location name</t>
   </si>
   <si>
     <t>Name of the location as used by humans. Does not need to be unique.</t>
@@ -826,7 +826,7 @@
 </t>
   </si>
   <si>
-    <t>Contact details of the location</t>
+    <t>Location telecom</t>
   </si>
   <si>
     <t>The contact details of communication devices available at the location. This can include phone numbers, fax numbers, mobile numbers, email addresses and web sites.</t>
@@ -838,7 +838,7 @@
     <t>Location.address</t>
   </si>
   <si>
-    <t xml:space="preserve">Address
+    <t xml:space="preserve">Address {http://hl7.eu/fhir/base/StructureDefinition/Address-eu}
 </t>
   </si>
   <si>
@@ -860,7 +860,7 @@
     <t>Location.physicalType</t>
   </si>
   <si>
-    <t>Physical form of the location</t>
+    <t>Location type</t>
   </si>
   <si>
     <t>Physical form of the location, e.g. building, room, vehicle, road.</t>
@@ -1404,7 +1404,7 @@
     <col min="8" max="8" width="14.625" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.98828125" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="22.921875" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="59.69140625" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>

--- a/StructureDefinition-chul-location.xlsx
+++ b/StructureDefinition-chul-location.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-09-12T14:17:00+02:00</t>
+    <t>2026-02-04T18:27:09+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
